--- a/artfynd/A 58039-2019 artfynd.xlsx
+++ b/artfynd/A 58039-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58039-2019 artfynd.xlsx
+++ b/artfynd/A 58039-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2472,150 +2472,6 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>90668253</v>
-      </c>
-      <c r="B17" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>219955</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Slåttergubbe</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Arnica montana</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Dampetorp, väst om, Nrk</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>498253.257271082</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6529666.87090914</v>
-      </c>
-      <c r="S17" t="n">
-        <v>50</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Askersund</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Lerbäck</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>T-Ask-0208</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>1982-07-05</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>1982-07-05</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2 stänglar</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Stor inäga, före detta sågplats.</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Henrik Josefsson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Gunnar Hallin</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
